--- a/Reporte/ReportesSigre.xlsx
+++ b/Reporte/ReportesSigre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sigreweb-main\sigreweb-main\app\Reporte\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jordan\Documents\SigreWeb\app\Reporte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82ABCE75-5711-48E2-856D-BF16A2CB2826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5962F8-9431-4C16-AF24-D3BEAAC1CE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4481B342-BB1C-481E-A30A-ED1416DC2C19}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4481B342-BB1C-481E-A30A-ED1416DC2C19}"/>
   </bookViews>
   <sheets>
     <sheet name="BT" sheetId="1" r:id="rId1"/>
@@ -345,7 +345,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -412,15 +412,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="medium">
@@ -1027,99 +1018,76 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1129,22 +1097,22 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1156,10 +1124,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1168,315 +1136,298 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="10" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1828,404 +1779,387 @@
     <col min="8" max="8" width="1.5703125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="2.28515625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="4.85546875" customWidth="1"/>
-    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="76.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="72.28515625" customWidth="1"/>
+    <col min="13" max="13" width="37" customWidth="1"/>
     <col min="14" max="15" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36"/>
+      <c r="A1" s="27"/>
     </row>
     <row r="2" spans="1:22" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K2" s="1"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="122"/>
+      <c r="L2" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="139" t="s">
+      <c r="M2" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="140"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="144"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="114"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K4" s="4"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="8" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="145"/>
-      <c r="O4" s="146"/>
+      <c r="M4" s="115"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K5" s="4"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="8" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="145"/>
-      <c r="O5" s="146"/>
+      <c r="M5" s="115"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K6" s="4"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="8" t="s">
+      <c r="K6" s="2"/>
+      <c r="L6" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="141"/>
-      <c r="O6" s="142"/>
+      <c r="M6" s="115"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="62" t="s">
+      <c r="K7" s="3"/>
+      <c r="L7" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="60"/>
+      <c r="M7" s="116"/>
     </row>
     <row r="8" spans="1:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="127" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="130" t="s">
+      <c r="C8" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="136" t="s">
+      <c r="D8" s="132" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="133" t="s">
+      <c r="E8" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="K8" s="111"/>
-      <c r="L8" s="109" t="s">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="121" t="s">
         <v>29</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="124"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="108"/>
     </row>
     <row r="9" spans="1:22" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="128"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="134"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="91" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="130"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="M9" s="120"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="122"/>
-      <c r="V9" s="37"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="106"/>
+      <c r="V9" s="28"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="128"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="137"/>
-      <c r="E10" s="134"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="K10" s="81"/>
-      <c r="L10" s="61" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="130"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="75"/>
-      <c r="N10" s="64"/>
-      <c r="O10" s="69"/>
-      <c r="V10" s="37"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="58"/>
+      <c r="V10" s="28"/>
     </row>
     <row r="11" spans="1:22" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="128"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="137"/>
-      <c r="E11" s="134"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="K11" s="84">
+      <c r="A11" s="7"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="130"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="K11" s="73">
         <v>6002</v>
       </c>
-      <c r="L11" s="54" t="s">
+      <c r="L11" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="75"/>
-      <c r="N11" s="64"/>
-      <c r="O11" s="69"/>
-      <c r="V11" s="37"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="58"/>
+      <c r="V11" s="28"/>
     </row>
     <row r="12" spans="1:22" ht="55.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="129"/>
-      <c r="C12" s="44">
+      <c r="A12" s="7"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="35">
         <v>0</v>
       </c>
-      <c r="D12" s="138"/>
-      <c r="E12" s="135"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="K12" s="84">
+      <c r="D12" s="134"/>
+      <c r="E12" s="131"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="K12" s="73">
         <v>6004</v>
       </c>
-      <c r="L12" s="54" t="s">
+      <c r="L12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="M12" s="75"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="69"/>
-      <c r="V12" s="37"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="58"/>
+      <c r="V12" s="28"/>
     </row>
     <row r="13" spans="1:22" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="33">
+      <c r="A13" s="7"/>
+      <c r="B13" s="24">
         <v>6002</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="39"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="K13" s="85">
+      <c r="C13" s="34"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="30"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="K13" s="74">
         <v>6006</v>
       </c>
-      <c r="L13" s="54" t="s">
+      <c r="L13" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="75"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="69"/>
-      <c r="V13" s="37"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="58"/>
+      <c r="V13" s="28"/>
     </row>
     <row r="14" spans="1:22" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="26">
+      <c r="A14" s="8"/>
+      <c r="B14" s="17">
         <v>6004</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="40"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="K14" s="86">
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="31"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="K14" s="75">
         <v>6008</v>
       </c>
-      <c r="L14" s="82" t="s">
+      <c r="L14" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="M14" s="76"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="70"/>
-      <c r="V14" s="38"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="59"/>
+      <c r="V14" s="29"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="26">
+      <c r="A15" s="9"/>
+      <c r="B15" s="17">
         <v>6006</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="40"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="91" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="31"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="M15" s="77"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="68"/>
-      <c r="V15" s="38"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="57"/>
+      <c r="V15" s="29"/>
     </row>
     <row r="16" spans="1:22" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="26">
+      <c r="A16" s="9"/>
+      <c r="B16" s="17">
         <v>6008</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="40"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="K16" s="86">
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="31"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="K16" s="75">
         <v>6024</v>
       </c>
-      <c r="L16" s="61" t="s">
+      <c r="L16" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="75"/>
-      <c r="N16" s="64"/>
-      <c r="O16" s="69"/>
-      <c r="V16" s="38"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="58"/>
+      <c r="V16" s="29"/>
     </row>
     <row r="17" spans="1:22" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="26">
+      <c r="A17" s="9"/>
+      <c r="B17" s="17">
         <v>6024</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="40"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="K17" s="89"/>
-      <c r="L17" s="61" t="s">
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="31"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="78"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="71"/>
-      <c r="V17" s="38"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="60"/>
+      <c r="V17" s="29"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="26">
+      <c r="A18" s="8"/>
+      <c r="B18" s="17">
         <v>6026</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="40"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="91" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="31"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="M18" s="77"/>
-      <c r="N18" s="63"/>
-      <c r="O18" s="68"/>
-      <c r="V18" s="38"/>
+      <c r="M18" s="66"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="57"/>
+      <c r="V18" s="29"/>
     </row>
     <row r="19" spans="1:22" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="17">
         <v>6028</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="40"/>
-      <c r="K19" s="90">
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="31"/>
+      <c r="K19" s="79">
         <v>6026</v>
       </c>
-      <c r="L19" s="61" t="s">
+      <c r="L19" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="M19" s="75"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="69"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="58"/>
     </row>
     <row r="20" spans="1:22" ht="43.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="42"/>
-      <c r="K20" s="86">
+      <c r="C20" s="21"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
+      <c r="K20" s="75">
         <v>6028</v>
       </c>
-      <c r="L20" s="94" t="s">
+      <c r="L20" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="M20" s="75"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="69"/>
+      <c r="M20" s="64"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="58"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="77"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="68"/>
+      <c r="A21" s="8"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="57"/>
     </row>
     <row r="22" spans="1:22" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K22" s="93"/>
-      <c r="L22" s="115" t="s">
+      <c r="K22" s="82"/>
+      <c r="L22" s="101" t="s">
         <v>34</v>
       </c>
-      <c r="M22" s="112"/>
-      <c r="N22" s="113"/>
-      <c r="O22" s="114"/>
+      <c r="M22" s="98"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="100"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="106" t="s">
+      <c r="A23" s="11"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="M23" s="79"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="72"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="61"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="32"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="83" t="s">
+      <c r="A24" s="23"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="80"/>
-      <c r="N24" s="73"/>
-      <c r="O24" s="74"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="63"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
+      <c r="A28" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
+      <c r="A29" s="16"/>
     </row>
     <row r="33" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="3:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="3:9" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="3:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="4">
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="D8:D12"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N5:O5"/>
   </mergeCells>
   <conditionalFormatting sqref="L8">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
@@ -2252,288 +2186,271 @@
     <col min="10" max="10" width="4.85546875" customWidth="1"/>
     <col min="11" max="11" width="7.7109375" customWidth="1"/>
     <col min="12" max="12" width="80.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.28515625" customWidth="1"/>
     <col min="14" max="15" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:15" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K2" s="1"/>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="147" t="s">
+      <c r="M2" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="148"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="143"/>
-      <c r="O3" s="144"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="113"/>
+      <c r="M3" s="114"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K4" s="4"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="8" t="s">
+      <c r="K4" s="2"/>
+      <c r="L4" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="145"/>
-      <c r="O4" s="146"/>
+      <c r="M4" s="115"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K5" s="4"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="8" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="145"/>
-      <c r="O5" s="146"/>
+      <c r="M5" s="115"/>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="149" t="s">
+      <c r="B6" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="152" t="s">
+      <c r="C6" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="155" t="s">
+      <c r="D6" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="157" t="s">
+      <c r="E6" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="8" t="s">
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="141"/>
-      <c r="O6" s="142"/>
+      <c r="M6" s="115"/>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="150"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="I7" s="37"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="62" t="s">
+      <c r="B7" s="136"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="I7" s="28"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="N7" s="126"/>
-      <c r="O7" s="12"/>
+      <c r="M7" s="116"/>
     </row>
     <row r="8" spans="1:15" ht="18.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="150"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-      <c r="I8" s="37"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="I8" s="28"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="147"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="150"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-      <c r="I9" s="37"/>
-      <c r="K9" s="158" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="139"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="I9" s="28"/>
+      <c r="K9" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="118" t="s">
+      <c r="L9" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="154"/>
-      <c r="D10" s="150"/>
-      <c r="E10" s="150"/>
-      <c r="I10" s="37"/>
-      <c r="K10" s="159"/>
-      <c r="L10" s="117" t="s">
+      <c r="A10" s="37"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="136"/>
+      <c r="E10" s="136"/>
+      <c r="I10" s="28"/>
+      <c r="K10" s="145"/>
+      <c r="L10" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47"/>
-      <c r="B11" s="151"/>
-      <c r="C11" s="51">
+      <c r="A11" s="38"/>
+      <c r="B11" s="137"/>
+      <c r="C11" s="42">
         <v>0</v>
       </c>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="I11" s="37"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91" t="s">
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="I11" s="28"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="91"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="91"/>
+      <c r="M11" s="80"/>
+      <c r="N11" s="80"/>
+      <c r="O11" s="80"/>
     </row>
     <row r="12" spans="1:15" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
-      <c r="B12" s="102">
+      <c r="A12" s="39"/>
+      <c r="B12" s="91">
         <v>7002</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="37"/>
-      <c r="K12" s="102">
+      <c r="C12" s="34"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="28"/>
+      <c r="K12" s="91">
         <v>7002</v>
       </c>
-      <c r="L12" s="58" t="s">
+      <c r="L12" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
     </row>
     <row r="13" spans="1:15" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="107"/>
-      <c r="B13" s="103">
+      <c r="A13" s="96"/>
+      <c r="B13" s="92">
         <v>7004</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="K13" s="103">
+      <c r="C13" s="18"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="K13" s="92">
         <v>7004</v>
       </c>
-      <c r="L13" s="87" t="s">
+      <c r="L13" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="108"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="108"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="97"/>
     </row>
     <row r="14" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="103">
+      <c r="A14" s="39"/>
+      <c r="B14" s="92">
         <v>7006</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="K14" s="103">
+      <c r="C14" s="18"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="K14" s="92">
         <v>7006</v>
       </c>
-      <c r="L14" s="88" t="s">
+      <c r="L14" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
     </row>
     <row r="15" spans="1:15" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
-      <c r="B15" s="104">
+      <c r="A15" s="39"/>
+      <c r="B15" s="93">
         <v>7008</v>
       </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="97"/>
-      <c r="I15" s="38"/>
-      <c r="K15" s="103">
+      <c r="C15" s="84"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="86"/>
+      <c r="I15" s="29"/>
+      <c r="K15" s="92">
         <v>7008</v>
       </c>
-      <c r="L15" s="88" t="s">
+      <c r="L15" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="59"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="49"/>
-      <c r="B16" s="98" t="s">
+      <c r="A16" s="40"/>
+      <c r="B16" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="99"/>
-      <c r="D16" s="100"/>
-      <c r="E16" s="101"/>
-      <c r="I16" s="38"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="119" t="s">
+      <c r="C16" s="88"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="90"/>
+      <c r="I16" s="29"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="M16" s="125"/>
-      <c r="N16" s="125"/>
-      <c r="O16" s="125"/>
+      <c r="M16" s="109"/>
+      <c r="N16" s="109"/>
+      <c r="O16" s="109"/>
     </row>
     <row r="17" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="105"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="106" t="s">
+      <c r="A17" s="94"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="95" t="s">
         <v>30</v>
       </c>
-      <c r="M17" s="57"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="57"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="34" t="s">
+      <c r="A18" s="41"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="25">
+      <c r="A22" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
+      <c r="A23" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="N5:O5"/>
+  <mergeCells count="5">
     <mergeCell ref="B6:B11"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="D6:D11"/>
     <mergeCell ref="E6:E11"/>
-    <mergeCell ref="N6:O6"/>
     <mergeCell ref="K9:K10"/>
   </mergeCells>
   <conditionalFormatting sqref="K9">
